--- a/chart.xlsx
+++ b/chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f52a1b825f10857e/Desktop/ISLaba/site/labasite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_AD4DF75460589B3ACB7284B70F5A5BD05ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFE7307F-BCFE-496C-B48C-C4559D15BDAF}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="11_AD4DF75460589B3ACB7284B70F5A5BD05ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F7E15A9-9894-4463-85CE-700B8BAAD864}"/>
   <bookViews>
-    <workbookView xWindow="6470" yWindow="2520" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6400" yWindow="2520" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Электроника</t>
   </si>
@@ -64,19 +64,10 @@
     <t>Прибыль</t>
   </si>
   <si>
-    <t>Смартфон Vivo</t>
-  </si>
-  <si>
     <t>Сумма продаж</t>
   </si>
   <si>
-    <t>Стул Алексея навального</t>
-  </si>
-  <si>
     <t>Аксессуары</t>
-  </si>
-  <si>
-    <t>Попыт</t>
   </si>
 </sst>
 </file>
@@ -231,15 +222,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>13500</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>16500</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -528,15 +510,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
-                <c:pt idx="0">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>150</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -812,13 +785,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>20000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38500</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>22500</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3117,24 +3090,15 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>6000</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3">
-        <v>13500</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
-      </c>
-      <c r="B4">
-        <v>16500</v>
       </c>
     </row>
   </sheetData>
@@ -3171,79 +3135,25 @@
         <v>7</v>
       </c>
       <c r="G1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>20</v>
-      </c>
-      <c r="D2">
-        <v>1000</v>
-      </c>
-      <c r="E2">
-        <v>700</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
         <f>C2*D2</f>
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>3500</v>
-      </c>
-      <c r="E3">
-        <v>2000</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
         <f t="shared" ref="G3:G30" si="0">C3*D3</f>
-        <v>38500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>150</v>
-      </c>
-      <c r="D4">
-        <v>150</v>
-      </c>
-      <c r="E4">
-        <v>60</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>22500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">

--- a/chart.xlsx
+++ b/chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f52a1b825f10857e/Desktop/ISLaba/site/labasite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_AD4DF75460589B3ACB7284B70F5A5BD05ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F7E15A9-9894-4463-85CE-700B8BAAD864}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="11_AD4DF75460589B3ACB7284B70F5A5BD05ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA271B0B-5796-4021-95E9-EBB6049EF586}"/>
   <bookViews>
-    <workbookView xWindow="6400" yWindow="2520" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="110" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>Электроника</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>Аксессуары</t>
+  </si>
+  <si>
+    <t>Попыт</t>
   </si>
 </sst>
 </file>
@@ -222,6 +225,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
+                <c:pt idx="1">
+                  <c:v>13500</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -510,6 +516,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>150</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -785,7 +794,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>22500</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3095,6 +3104,9 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
+      <c r="B3">
+        <v>13500</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -3139,9 +3151,27 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>150</v>
+      </c>
+      <c r="D2">
+        <v>150</v>
+      </c>
+      <c r="E2">
+        <v>60</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
       <c r="G2">
         <f>C2*D2</f>
-        <v>0</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
